--- a/Отчёты/Gamma_098_Отчёт.xlsx
+++ b/Отчёты/Gamma_098_Отчёт.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>-71.957</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,79 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10.878</t>
+          <t>Отсутствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Pn (80 кэВ)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Pn (146 кэВ)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Pn (400 кэВ)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Pn (850 кэВ)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Pn (1500 кэВ)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Pn (2515 кэВ)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>516</t>
         </is>
       </c>
     </row>

--- a/Отчёты/Gamma_098_Отчёт.xlsx
+++ b/Отчёты/Gamma_098_Отчёт.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Отсутствует</t>
+          <t>-71.957</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Отсутствует</t>
+          <t>10.878</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
